--- a/docs/triton-learning/cards/triton-lesson-01-vector-add-oral.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-01-vector-add-oral.xlsx
@@ -36,16 +36,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">用 60 秒说明尾块 mask 的职责。</t>
+          <t xml:space="preserve">一个 Triton 向量 kernel 的最后一块只有部分位置有效，加载结果还可能参与归约，最终按条件写回。请用约 60 秒说明：mask 对局部形状、归约正确性和写回安全各负责什么？</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：mask 控制逐位置访存，不压缩局部 tensor。
-• [T#B#形状与读取]：结果形状跟随局部 pointer tensor；false lane 不读取，但逻辑位置仍保留。
-• [T#B#归约]：无效值可能进入归约，必须在归约前处理；store 无法修复已污染的结果。
-• [T#B#写回]：条件写回显式合并 boundary_mask 与 condition；合法地址的 false store 保留原值。
-[T#B,!c47f17#边界]：false predicate 的地址读写不发生；地址、谓词和调度仍可能有开销，有效 lane 仍按物理事务粒度访存。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：mask 逐位置控制访存，但局部 tensor 仍保留固定形状；要保证整条计算链正确，还必须分别处理归约中的无效值和写回时的地址边界。
+• [T#B#形状与读取]：load 的结果形状跟随该 program 的局部 pointer tensor。false 位置不读取对应地址，却仍占一个逻辑位置，不能当作已经被删除。
+• [T#B#归约]：归约会合并保留下来的位置。应先为无效项提供不影响该归约的值；store mask 无法修复此前已经被污染的归约结果。
+• [T#B#写回]：有条件写回时，把地址有效的 boundary_mask 与数值条件 condition 取逻辑与。对于合法目标地址，false store 不写入，也不会自动写零。
+[T#B,!c47f17#边界]：false predicate 禁止相应地址访问，但 program 仍可能执行地址计算和调度；有效访问仍受内存事务粒度影响，不能把 mask 当作零开销保证。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -62,17 +62,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">用 60 秒复盘一组微小性能差异。</t>
+          <t xml:space="preserve">比较 GPU 向量 kernel 的整块与尾块输入时，延迟差异很小，有效 GB/s 还出现反向变化。请用约 60 秒说明：从指标定义、采样口径和事前判据出发，怎样避免过度解释这组结果？</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：先说明测量对象和指标，再解释观测能支持到哪里。
-• [T#B#指标]：有效 GB/s 是有效字节数除以测量时间；上升可能来自分子或分母变化，不能直接证明物理带宽提升。
-• [T#B#采样]：do_bench 的 rep 是总采样预算，不把单个很短的计时间隔拉长。
-• [T#B#口径]：批量后求平均可能改变缓存和发射场景，应与单次结果分别解释。
-• [T#B#判据]：按事前反证条件报告原结果，再说明方法缺陷与后续改进，不事后改标准。
-[T#B,!c47f17#边界]：没有受控证据时，不把指标波动写成已证明的 GPU 优化。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：先明确比较的是哪种测量场景，再拆开有效工作量与耗时，最后按事前规则报告结果，并限制对 GPU 优化的因果推断。
+• [T#B#指标]：有效 GB/s 是算法规定的有效读写字节数除以测量时间；尾块工作量稍增或测得时间稍降，都可能使该比值上升，不能直接证明实际 DRAM 带宽提升。
+• [T#B#采样]：do_bench 的 rep 指整轮采样预算。增加预算不等于把每次短 kernel 的计时间隔拉长。
+• [T#B#批量口径]：把多次调用合在一个窗口后求平均，可以延长窗口，但可能改变缓存和发射条件；它与单次调用结果应分别解释。
+• [T#B#判据]：即使后来发现阈值不适合计时分辨率，也要保留事前规则下的判定，再说明方法局限并改进下一次实验。
+[T#B,!c47f17#边界]：现有证据只能支持与其测量设计相匹配的结论；没有受控证据时，不把微小波动写成已证明的 GPU 优化机制。</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">

--- a/docs/triton-learning/cards/triton-lesson-01-vector-add-oral.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-01-vector-add-oral.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -36,53 +36,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">一个 Triton 向量 kernel 的最后一块只有部分位置有效，加载结果还可能参与归约，最终按条件写回。请用约 60 秒说明：mask 对局部形状、归约正确性和写回安全各负责什么？</t>
+          <t xml:space="preserve">向面试官解释：一个 Triton 向量 kernel 的最后一块只有部分位置有效，加载结果还要参与归约，最后按条件写回。请用约 60 秒说明 mask 在读取与形状、归约、写回三处各负责什么。</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：mask 逐位置控制访存，但局部 tensor 仍保留固定形状；要保证整条计算链正确，还必须分别处理归约中的无效值和写回时的地址边界。
-• [T#B#形状与读取]：load 的结果形状跟随该 program 的局部 pointer tensor。false 位置不读取对应地址，却仍占一个逻辑位置，不能当作已经被删除。
-• [T#B#归约]：归约会合并保留下来的位置。应先为无效项提供不影响该归约的值；store mask 无法修复此前已经被污染的归约结果。
-• [T#B#写回]：有条件写回时，把地址有效的 boundary_mask 与数值条件 condition 取逻辑与。对于合法目标地址，false store 不写入，也不会自动写零。
-[T#B,!c47f17#边界]：false predicate 禁止相应地址访问，但 program 仍可能执行地址计算和调度；有效访问仍受内存事务粒度影响，不能把 mask 当作零开销保证。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：mask 逐位置控制访存，但不改变块的静态形状；要让整条计算链正确，还得分别处理归约里的无效值和写回时的地址边界。
+• [T#B#读取与形状]：load 结果的形状跟随该 program 的局部 pointer tensor；false 位置不读对应地址（访存带 predicate，不是事后优化），却仍占一个逻辑位置。
+• [T#B#归约]：归约会合并所有位置，所以先给无效位置填该归约的单位元，例如 sum 填 0、max 填负无穷；store mask 无法修复已被污染的归约结果。
+• [T#B#写回]：条件写回时把地址有效的 boundary mask 与数值条件取逻辑与，不靠填充值恰好通不过比较来防越界；合法地址上 false store 不写入，原值保留。
+[T#B,!c47f17#边界]：mask 关掉的只是 false lane 的访存，地址计算和调度仍有成本。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">局部 pointer 形状；false lane 读取语义；归约前处理无效值；boundary 与 condition；不等于零开销</t>
+          <t xml:space="preserve">形状来自局部 pointer tensor；false lane 不访存（predicate）；归约前填单位元；写回合并 boundary 与 condition</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triton 3.7.1 · L01 日志：mask 相关纠错与复述</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">比较 GPU 向量 kernel 的整块与尾块输入时，延迟差异很小，有效 GB/s 还出现反向变化。请用约 60 秒说明：从指标定义、采样口径和事前判据出发，怎样避免过度解释这组结果？</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：先明确比较的是哪种测量场景，再拆开有效工作量与耗时，最后按事前规则报告结果，并限制对 GPU 优化的因果推断。
-• [T#B#指标]：有效 GB/s 是算法规定的有效读写字节数除以测量时间；尾块工作量稍增或测得时间稍降，都可能使该比值上升，不能直接证明实际 DRAM 带宽提升。
-• [T#B#采样]：do_bench 的 rep 指整轮采样预算。增加预算不等于把每次短 kernel 的计时间隔拉长。
-• [T#B#批量口径]：把多次调用合在一个窗口后求平均，可以延长窗口，但可能改变缓存和发射条件；它与单次调用结果应分别解释。
-• [T#B#判据]：即使后来发现阈值不适合计时分辨率，也要保留事前规则下的判定，再说明方法局限并改进下一次实验。
-[T#B,!c47f17#边界]：现有证据只能支持与其测量设计相匹配的结论；没有受控证据时，不把微小波动写成已证明的 GPU 优化机制。</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有效 GB/s 的分子分母；总预算与单次间隔；批量场景变化；保留事前判据；有边界的因果结论</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Triton 3.7.1 · L01 日志：基础 Benchmark 复盘</t>
+          <t xml:space="preserve">Triton 3.7.1 · L01 日志：mask 相关要点与复述</t>
         </is>
       </c>
     </row>
